--- a/data/trans_orig/P16A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455589</t>
+          <t>456006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468639</t>
+          <t>468696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290403</t>
+          <t>289933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302097</t>
+          <t>302263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751644</t>
+          <t>751756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768679</t>
+          <t>768904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351122</t>
+          <t>351472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364024</t>
+          <t>363389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357307</t>
+          <t>356802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368893</t>
+          <t>368948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714385</t>
+          <t>714242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731077</t>
+          <t>730847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527431</t>
+          <t>528019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538871</t>
+          <t>538795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>155385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164912</t>
+          <t>164882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687347</t>
+          <t>687115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701841</t>
+          <t>701594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>41954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,47 +1777,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24292</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15718</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35708</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24292</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15027</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34036</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70850</t>
+          <t>69616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1196273</t>
+          <t>1196380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1217890</t>
+          <t>1217599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,47 +1890,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>689993</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>678577</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>698567</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>689993</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>680249</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>699258</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1881770</t>
+          <t>1883004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910718</t>
+          <t>1912223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43748</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330662</t>
+          <t>330862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344304</t>
+          <t>344219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537338</t>
+          <t>535457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555624</t>
+          <t>555047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>874541</t>
+          <t>874677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>896615</t>
+          <t>896871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90962</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56309</t>
+          <t>56074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87827</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1157798</t>
+          <t>1160206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1190557</t>
+          <t>1193013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1459133</t>
+          <t>1457316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1490651</t>
+          <t>1490886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>48391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80430</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119030</t>
+          <t>120437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165976</t>
+          <t>167558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176279</t>
+          <t>177889</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>233182</t>
+          <t>236476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3188742</t>
+          <t>3186732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3218567</t>
+          <t>3220781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3212148</t>
+          <t>3210566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3259094</t>
+          <t>3257687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6414114</t>
+          <t>6410820</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6471017</t>
+          <t>6469407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>21450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417843</t>
+          <t>418118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433224</t>
+          <t>433194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292922</t>
+          <t>293004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308662</t>
+          <t>308371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717067</t>
+          <t>719175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739682</t>
+          <t>739801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396590</t>
+          <t>396274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411937</t>
+          <t>411842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321054</t>
+          <t>322129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332316</t>
+          <t>332371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721962</t>
+          <t>722798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742117</t>
+          <t>742274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>595162</t>
+          <t>595591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614378</t>
+          <t>614903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237100</t>
+          <t>236624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251592</t>
+          <t>251558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>838124</t>
+          <t>838302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861576</t>
+          <t>861934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>68227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128028</t>
+          <t>1127509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147335</t>
+          <t>1146371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719876</t>
+          <t>719914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743862</t>
+          <t>743256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854792</t>
+          <t>1855547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886432</t>
+          <t>1886034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>50940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81755</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61011</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>94358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489457</t>
+          <t>490729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503597</t>
+          <t>503736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676613</t>
+          <t>677344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708583</t>
+          <t>707428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1169968</t>
+          <t>1173577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1206924</t>
+          <t>1206796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76438</t>
+          <t>76931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116906</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75478</t>
+          <t>77525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114828</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>988350</t>
+          <t>988991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1028818</t>
+          <t>1028325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1256270</t>
+          <t>1257084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1295620</t>
+          <t>1293573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53078</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88872</t>
+          <t>86945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191227</t>
+          <t>194184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>253119</t>
+          <t>252307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259227</t>
+          <t>253367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327175</t>
+          <t>323436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3324200</t>
+          <t>3326127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3359994</t>
+          <t>3361765</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3283856</t>
+          <t>3284668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3345748</t>
+          <t>3342791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6622872</t>
+          <t>6626611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6690820</t>
+          <t>6696680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407288</t>
+          <t>407953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423358</t>
+          <t>423208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327112</t>
+          <t>328385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341341</t>
+          <t>341529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743008</t>
+          <t>742794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762504</t>
+          <t>762361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361593</t>
+          <t>362013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373298</t>
+          <t>373337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350356</t>
+          <t>351471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365432</t>
+          <t>365844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718525</t>
+          <t>718696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736506</t>
+          <t>736725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500769</t>
+          <t>501650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515071</t>
+          <t>515390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141858</t>
+          <t>142022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157447</t>
+          <t>158408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648546</t>
+          <t>649190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>669972</t>
+          <t>670362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>50533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65149</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>100818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1097975</t>
+          <t>1099105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1124297</t>
+          <t>1122761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765867</t>
+          <t>765932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>792682</t>
+          <t>792401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873710</t>
+          <t>1874696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910365</t>
+          <t>1909597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57752</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90406</t>
+          <t>92798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74251</t>
+          <t>74448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111969</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592638</t>
+          <t>590527</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609133</t>
+          <t>608672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>647838</t>
+          <t>645446</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>680492</t>
+          <t>679511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246981</t>
+          <t>1246603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1284699</t>
+          <t>1284502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91411</t>
+          <t>90556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133988</t>
+          <t>131987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91495</t>
+          <t>92640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>135023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279619</t>
+          <t>279737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>948037</t>
+          <t>950038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>990614</t>
+          <t>991469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1231132</t>
+          <t>1234147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1277675</t>
+          <t>1276530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72807</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111241</t>
+          <t>109919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235729</t>
+          <t>236102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>299234</t>
+          <t>302068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319359</t>
+          <t>319251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>397201</t>
+          <t>396441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3274481</t>
+          <t>3275803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3312915</t>
+          <t>3313946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3232362</t>
+          <t>3229528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3295867</t>
+          <t>3295494</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6520117</t>
+          <t>6520877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6597959</t>
+          <t>6598067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>35127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65644</t>
+          <t>66090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468174</t>
+          <t>468141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487510</t>
+          <t>487713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411038</t>
+          <t>412340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428590</t>
+          <t>428213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887035</t>
+          <t>886589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>912312</t>
+          <t>912211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38968</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63273</t>
+          <t>63608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423544</t>
+          <t>423375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439918</t>
+          <t>439670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341809</t>
+          <t>342666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359400</t>
+          <t>359326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771520</t>
+          <t>771185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>795825</t>
+          <t>794823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>44070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69873</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624816</t>
+          <t>624194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659970</t>
+          <t>660481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139167</t>
+          <t>139378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151669</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>765302</t>
+          <t>765838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817134</t>
+          <t>815401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>51015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75161</t>
+          <t>78232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77430</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82656</t>
+          <t>85761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>142711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>959658</t>
+          <t>956587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>985349</t>
+          <t>983804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>899607</t>
+          <t>901137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945370</t>
+          <t>949806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871199</t>
+          <t>1869144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929199</t>
+          <t>1926094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87143</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143238</t>
+          <t>147207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120242</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172172</t>
+          <t>171636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436420</t>
+          <t>436727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454726</t>
+          <t>455524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>695598</t>
+          <t>691629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>751693</t>
+          <t>748641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140222</t>
+          <t>1140758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192152</t>
+          <t>1194634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84118</t>
+          <t>84369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112297</t>
+          <t>114195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123561</t>
+          <t>125829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213482</t>
+          <t>217360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237539</t>
+          <t>237526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>647855</t>
+          <t>645957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>676034</t>
+          <t>675783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877098</t>
+          <t>874830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>911058</t>
+          <t>910131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131756</t>
+          <t>130752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195115</t>
+          <t>197672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286637</t>
+          <t>289134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>393183</t>
+          <t>392082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448933</t>
+          <t>449554</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>572615</t>
+          <t>567470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3179459</t>
+          <t>3176902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3242818</t>
+          <t>3243822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3179799</t>
+          <t>3180900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3286345</t>
+          <t>3283848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6374941</t>
+          <t>6380086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6498623</t>
+          <t>6498002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>28705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456006</t>
+          <t>456514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468696</t>
+          <t>469337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289933</t>
+          <t>290024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302263</t>
+          <t>302407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751756</t>
+          <t>751752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768904</t>
+          <t>768601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351472</t>
+          <t>351760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363389</t>
+          <t>364067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356802</t>
+          <t>358023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368948</t>
+          <t>369008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714242</t>
+          <t>715411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730847</t>
+          <t>730932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528019</t>
+          <t>528448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538795</t>
+          <t>538968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155385</t>
+          <t>154597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164882</t>
+          <t>164958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687115</t>
+          <t>687209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701594</t>
+          <t>701554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40397</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69616</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1196380</t>
+          <t>1196455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1217599</t>
+          <t>1218446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678577</t>
+          <t>676899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698567</t>
+          <t>697865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883004</t>
+          <t>1882960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912223</t>
+          <t>1910966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43612</t>
+          <t>44024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330862</t>
+          <t>330521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535457</t>
+          <t>536746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555047</t>
+          <t>555809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>874677</t>
+          <t>874265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>896871</t>
+          <t>896340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55747</t>
+          <t>57136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88554</t>
+          <t>88514</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>56942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1160206</t>
+          <t>1160246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1193013</t>
+          <t>1191624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1457316</t>
+          <t>1457226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1490886</t>
+          <t>1490018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48391</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82440</t>
+          <t>83127</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120437</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167558</t>
+          <t>167186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177889</t>
+          <t>177686</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>236476</t>
+          <t>235105</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3186732</t>
+          <t>3186045</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3220781</t>
+          <t>3217750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3210566</t>
+          <t>3210938</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3257687</t>
+          <t>3259537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6410820</t>
+          <t>6412191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6469407</t>
+          <t>6469610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418118</t>
+          <t>417448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433194</t>
+          <t>433207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293004</t>
+          <t>292202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308371</t>
+          <t>308471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719175</t>
+          <t>718325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739801</t>
+          <t>738549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396274</t>
+          <t>397026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411842</t>
+          <t>411909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322129</t>
+          <t>321983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722798</t>
+          <t>724371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742274</t>
+          <t>742045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30747</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +4104,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>32211</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>21817</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>45286</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>32211</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>45974</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>595591</t>
+          <t>595132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614903</t>
+          <t>614732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236624</t>
+          <t>237431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251558</t>
+          <t>250693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +4217,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>852065</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>838990</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>862459</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,53%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>852065</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>838302</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>861934</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45729</t>
+          <t>45380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68227</t>
+          <t>68441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1127509</t>
+          <t>1127782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146371</t>
+          <t>1146963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719914</t>
+          <t>720263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743256</t>
+          <t>744103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1855547</t>
+          <t>1855333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886034</t>
+          <t>1885717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>49885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>81533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>60970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94358</t>
+          <t>94119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490729</t>
+          <t>490810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503736</t>
+          <t>503783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677344</t>
+          <t>676835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707428</t>
+          <t>708483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1173577</t>
+          <t>1173816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1206796</t>
+          <t>1206965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76931</t>
+          <t>75569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>116059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77525</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>117095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>988991</t>
+          <t>989197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1028325</t>
+          <t>1029687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1257084</t>
+          <t>1254003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1293573</t>
+          <t>1294987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51307</t>
+          <t>52567</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86945</t>
+          <t>89308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194184</t>
+          <t>196429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252307</t>
+          <t>251688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253367</t>
+          <t>255701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323436</t>
+          <t>325111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3326127</t>
+          <t>3323764</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3361765</t>
+          <t>3360505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3284668</t>
+          <t>3285287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3342791</t>
+          <t>3340546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6626611</t>
+          <t>6624936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6696680</t>
+          <t>6694346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>408726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423208</t>
+          <t>423361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328385</t>
+          <t>328134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341529</t>
+          <t>341927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742794</t>
+          <t>742450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762361</t>
+          <t>762415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>362208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373337</t>
+          <t>373908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351471</t>
+          <t>351310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365844</t>
+          <t>365426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718696</t>
+          <t>717886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736725</t>
+          <t>736775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>39690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501650</t>
+          <t>500445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515390</t>
+          <t>515241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142022</t>
+          <t>143037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158408</t>
+          <t>158307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649190</t>
+          <t>648346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670362</t>
+          <t>669312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26877</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>33592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>57937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>64749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100818</t>
+          <t>100430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1099105</t>
+          <t>1099832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1122761</t>
+          <t>1124549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765932</t>
+          <t>767939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>792401</t>
+          <t>792284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874696</t>
+          <t>1875084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1909597</t>
+          <t>1910765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30179</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>58292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92798</t>
+          <t>92535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74448</t>
+          <t>76049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112347</t>
+          <t>112663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590527</t>
+          <t>591799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608672</t>
+          <t>609164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645446</t>
+          <t>645709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679511</t>
+          <t>679952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246603</t>
+          <t>1246287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1284502</t>
+          <t>1282901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131987</t>
+          <t>133120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92640</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135023</t>
+          <t>136990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279737</t>
+          <t>278748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>950038</t>
+          <t>948905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>991469</t>
+          <t>991618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1234147</t>
+          <t>1232180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1276530</t>
+          <t>1276672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71776</t>
+          <t>72365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109919</t>
+          <t>109070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236102</t>
+          <t>235602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302068</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319251</t>
+          <t>319236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396441</t>
+          <t>397169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3275803</t>
+          <t>3276652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3313946</t>
+          <t>3313357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3229528</t>
+          <t>3229377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3295494</t>
+          <t>3295994</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6520877</t>
+          <t>6520149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6598067</t>
+          <t>6598082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,27 +8703,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66090</t>
+          <t>72073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>479252</t>
+          <t>523754</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468141</t>
+          <t>512496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487713</t>
+          <t>532204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>421652</t>
+          <t>460244</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412340</t>
+          <t>450456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428213</t>
+          <t>467886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,22 +8816,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>900904</t>
+          <t>983998</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>886589</t>
+          <t>966956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>912211</t>
+          <t>996097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28838</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>42754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63608</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>432925</t>
+          <t>463273</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423375</t>
+          <t>453399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439670</t>
+          <t>470192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>389373</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342666</t>
+          <t>380389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359326</t>
+          <t>397618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>784912</t>
+          <t>852646</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771185</t>
+          <t>837410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794823</t>
+          <t>863481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44070</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45540</t>
+          <t>49789</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>39235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>65084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643304</t>
+          <t>444164</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624194</t>
+          <t>432645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660481</t>
+          <t>452816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146332</t>
+          <t>165156</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139378</t>
+          <t>157196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152324</t>
+          <t>171157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>789635</t>
+          <t>609320</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>765838</t>
+          <t>594025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815401</t>
+          <t>619874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78232</t>
+          <t>82891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>51223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>74616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>118771</t>
+          <t>129209</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>112352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142711</t>
+          <t>149052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>972866</t>
+          <t>1064602</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>956587</t>
+          <t>1048952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983804</t>
+          <t>1078226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>920219</t>
+          <t>797602</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>901137</t>
+          <t>784954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>949806</t>
+          <t>808347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1893084</t>
+          <t>1862204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1869144</t>
+          <t>1842361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926094</t>
+          <t>1879061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977037</t>
+          <t>859570</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977037</t>
+          <t>859570</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977037</t>
+          <t>859570</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011855</t>
+          <t>1991413</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011855</t>
+          <t>1991413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011855</t>
+          <t>1991413</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>120962</t>
+          <t>126020</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90195</t>
+          <t>112001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147207</t>
+          <t>144304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147647</t>
+          <t>155772</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117760</t>
+          <t>137926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171636</t>
+          <t>177649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>446874</t>
+          <t>536729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436727</t>
+          <t>524828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455524</t>
+          <t>545522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>717874</t>
+          <t>703399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>691629</t>
+          <t>685115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>748641</t>
+          <t>717418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1164747</t>
+          <t>1240128</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140758</t>
+          <t>1218251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1194634</t>
+          <t>1257974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312394</t>
+          <t>1395900</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312394</t>
+          <t>1395900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312394</t>
+          <t>1395900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>97860</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84369</t>
+          <t>91403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114195</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>115774</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>96964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125829</t>
+          <t>136873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232413</t>
+          <t>228140</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217360</t>
+          <t>214473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237526</t>
+          <t>233387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>662292</t>
+          <t>736307</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>645957</t>
+          <t>720573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>675783</t>
+          <t>751590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>894705</t>
+          <t>964447</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>874830</t>
+          <t>943348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910131</t>
+          <t>983257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130752</t>
+          <t>158195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197672</t>
+          <t>207416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>352627</t>
+          <t>378953</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>289134</t>
+          <t>351082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>392082</t>
+          <t>411570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519568</t>
+          <t>559284</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>449554</t>
+          <t>520697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>567470</t>
+          <t>602747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3207633</t>
+          <t>3260662</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3176902</t>
+          <t>3233577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3243822</t>
+          <t>3282798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3220355</t>
+          <t>3252079</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3180900</t>
+          <t>3219462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3283848</t>
+          <t>3279950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6427988</t>
+          <t>6512742</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6380086</t>
+          <t>6469279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6498002</t>
+          <t>6551329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572982</t>
+          <t>3631032</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572982</t>
+          <t>3631032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572982</t>
+          <t>3631032</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947556</t>
+          <t>7072026</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947556</t>
+          <t>7072026</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947556</t>
+          <t>7072026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
